--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/HAWAII_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/HAWAII_2016.xlsx
@@ -1291,7 +1291,7 @@
         <v>16</v>
       </c>
       <c r="D52">
-        <v>0.09142857142857143</v>
+        <v>0.09142857142857144</v>
       </c>
     </row>
     <row r="53">
